--- a/data/trans_camb/IP18A02-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP18A02-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 15,29</t>
+          <t>-4,07; 16,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 12,66</t>
+          <t>-8,99; 13,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,17; 29,31</t>
+          <t>-18,59; 27,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 7,38</t>
+          <t>-13,69; 7,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 11,34</t>
+          <t>-11,64; 9,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,91; 11,6</t>
+          <t>-23,44; 14,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 8,63</t>
+          <t>-6,34; 8,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 9,32</t>
+          <t>-6,98; 9,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-18,4; 9,85</t>
+          <t>-18,88; 8,28</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,77; 117,09</t>
+          <t>-18,27; 136,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-43,99; 92,76</t>
+          <t>-40,0; 112,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 227,6</t>
+          <t>-100,0; 183,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-53,26; 50,52</t>
+          <t>-53,39; 54,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-48,8; 78,97</t>
+          <t>-47,67; 60,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 90,37</t>
+          <t>-100,0; 105,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-26,45; 56,73</t>
+          <t>-28,32; 51,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,35; 61,4</t>
+          <t>-30,37; 58,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-87,73; 62,16</t>
+          <t>-88,23; 55,45</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 3,73</t>
+          <t>-5,36; 4,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,9; -0,8</t>
+          <t>-10,0; -0,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 10,08</t>
+          <t>-8,69; 10,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 2,94</t>
+          <t>-5,06; 2,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 5,33</t>
+          <t>-4,0; 5,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 11,29</t>
+          <t>-4,3; 10,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 2,42</t>
+          <t>-4,12; 2,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 1,2</t>
+          <t>-5,09; 0,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 7,62</t>
+          <t>-4,66; 7,41</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,04; 17,84</t>
+          <t>-22,01; 21,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,7; -4,53</t>
+          <t>-39,3; -1,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-37,28; 48,08</t>
+          <t>-35,4; 47,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,92; 17,91</t>
+          <t>-25,32; 17,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 31,89</t>
+          <t>-18,8; 30,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,66; 65,3</t>
+          <t>-21,84; 65,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,66; 12,65</t>
+          <t>-18,44; 12,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-22,33; 6,68</t>
+          <t>-23,25; 5,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-21,81; 40,43</t>
+          <t>-22,27; 37,83</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,81; -2,47</t>
+          <t>-18,22; -2,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 5,26</t>
+          <t>-11,8; 4,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-25,49; -4,3</t>
+          <t>-25,49; -5,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 7,32</t>
+          <t>-9,06; 6,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 2,48</t>
+          <t>-12,45; 3,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,88; 6,33</t>
+          <t>-18,82; 6,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,45; 0,1</t>
+          <t>-11,11; -0,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 1,09</t>
+          <t>-10,03; 0,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-19,57; -3,19</t>
+          <t>-19,33; -2,18</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-57,1; -11,0</t>
+          <t>-56,08; -10,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-37,69; 22,62</t>
+          <t>-37,59; 18,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-85,66; -15,18</t>
+          <t>-85,6; -17,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-30,66; 36,52</t>
+          <t>-31,35; 34,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-42,85; 12,55</t>
+          <t>-42,2; 16,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-70,03; 30,99</t>
+          <t>-70,22; 31,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-38,18; 1,47</t>
+          <t>-37,75; 0,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-36,54; 4,58</t>
+          <t>-33,98; 2,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-70,08; -13,21</t>
+          <t>-70,13; -8,03</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 1,51</t>
+          <t>-6,34; 1,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,2; -0,95</t>
+          <t>-8,35; -0,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 3,36</t>
+          <t>-10,55; 3,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 2,27</t>
+          <t>-4,66; 2,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 2,66</t>
+          <t>-4,18; 2,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 5,55</t>
+          <t>-6,8; 6,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 0,71</t>
+          <t>-4,41; 0,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 0,1</t>
+          <t>-5,27; -0,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 2,15</t>
+          <t>-7,05; 1,99</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-24,46; 7,67</t>
+          <t>-24,08; 8,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-32,55; -4,29</t>
+          <t>-32,78; -3,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-45,47; 14,95</t>
+          <t>-43,12; 14,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-22,61; 12,03</t>
+          <t>-21,42; 12,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,55; 13,98</t>
+          <t>-19,13; 15,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-31,41; 28,85</t>
+          <t>-32,16; 32,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,28; 3,43</t>
+          <t>-19,21; 3,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-21,63; 0,51</t>
+          <t>-22,41; -0,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-32,07; 10,25</t>
+          <t>-31,17; 9,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A02-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP18A02-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 16,73</t>
+          <t>-4,89; 15,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 13,99</t>
+          <t>-8,54; 13,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,59; 27,39</t>
+          <t>-19,69; 24,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 7,69</t>
+          <t>-12,53; 7,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 9,46</t>
+          <t>-11,17; 10,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,44; 14,71</t>
+          <t>-23,77; 13,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 8,03</t>
+          <t>-6,25; 8,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 9,02</t>
+          <t>-7,19; 8,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-18,88; 8,28</t>
+          <t>-18,76; 9,59</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,27; 136,23</t>
+          <t>-21,59; 126,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-40,0; 112,53</t>
+          <t>-39,74; 110,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 183,88</t>
+          <t>-100,0; 180,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-53,39; 54,93</t>
+          <t>-49,43; 49,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-47,67; 60,46</t>
+          <t>-45,54; 71,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 105,8</t>
+          <t>-100,0; 134,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-28,32; 51,46</t>
+          <t>-26,49; 54,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,37; 58,01</t>
+          <t>-33,05; 54,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-88,23; 55,45</t>
+          <t>-88,59; 65,87</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 4,32</t>
+          <t>-5,72; 4,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,0; -0,42</t>
+          <t>-9,72; -0,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 10,28</t>
+          <t>-8,39; 10,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 2,99</t>
+          <t>-5,34; 2,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 5,27</t>
+          <t>-3,13; 5,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 10,82</t>
+          <t>-4,67; 11,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 2,4</t>
+          <t>-4,09; 1,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 0,98</t>
+          <t>-5,41; 0,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 7,41</t>
+          <t>-4,32; 7,89</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-22,01; 21,84</t>
+          <t>-22,94; 20,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,3; -1,76</t>
+          <t>-38,62; -1,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-35,4; 47,31</t>
+          <t>-35,27; 47,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,32; 17,61</t>
+          <t>-25,59; 19,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,8; 30,93</t>
+          <t>-15,69; 31,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,84; 65,24</t>
+          <t>-23,58; 66,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,44; 12,5</t>
+          <t>-18,73; 10,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,25; 5,3</t>
+          <t>-24,16; 4,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-22,27; 37,83</t>
+          <t>-20,39; 41,25</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,22; -2,54</t>
+          <t>-18,03; -1,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,8; 4,24</t>
+          <t>-12,37; 4,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-25,49; -5,26</t>
+          <t>-26,56; -5,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 6,89</t>
+          <t>-9,96; 6,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 3,06</t>
+          <t>-12,73; 2,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,82; 6,81</t>
+          <t>-19,41; 5,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,11; -0,07</t>
+          <t>-11,37; 0,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 0,66</t>
+          <t>-10,01; 1,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-19,33; -2,18</t>
+          <t>-19,48; -2,36</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-56,08; -10,49</t>
+          <t>-56,35; -7,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-37,59; 18,36</t>
+          <t>-39,38; 17,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-85,6; -17,32</t>
+          <t>-88,14; -17,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-31,35; 34,9</t>
+          <t>-33,46; 33,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-42,2; 16,63</t>
+          <t>-44,0; 13,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-70,22; 31,2</t>
+          <t>-71,06; 26,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-37,75; 0,9</t>
+          <t>-39,05; 0,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-33,98; 2,99</t>
+          <t>-35,06; 4,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-70,13; -8,03</t>
+          <t>-69,23; -8,84</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 1,68</t>
+          <t>-6,25; 1,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,35; -0,78</t>
+          <t>-7,93; 0,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 3,27</t>
+          <t>-10,27; 3,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 2,27</t>
+          <t>-5,11; 2,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 2,94</t>
+          <t>-4,43; 2,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 6,03</t>
+          <t>-6,52; 5,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 0,69</t>
+          <t>-4,15; 0,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,27; -0,03</t>
+          <t>-5,05; 0,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 1,99</t>
+          <t>-7,48; 1,95</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-24,08; 8,58</t>
+          <t>-25,09; 7,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-32,78; -3,46</t>
+          <t>-31,69; -0,26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-43,12; 14,82</t>
+          <t>-42,69; 15,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-21,42; 12,4</t>
+          <t>-23,26; 11,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,13; 15,69</t>
+          <t>-19,78; 15,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-32,16; 32,56</t>
+          <t>-31,9; 27,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,21; 3,51</t>
+          <t>-18,46; 3,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-22,41; -0,25</t>
+          <t>-21,88; 0,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-31,17; 9,96</t>
+          <t>-33,55; 9,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A02-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP18A02-Estudios-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por control de salud periódico</t>
+          <t>Menores cuya última consulta médica fue por control de salud periódico</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-3,17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,88</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-13,62</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>5,3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1,81</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-3,06</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-3,17</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,88</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-13,37</t>
+          <t>-3,69</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-8,96</t>
+          <t>-9,48</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 15,71</t>
+          <t>-13,73; 7,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 13,31</t>
+          <t>-11,66; 11,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,69; 24,78</t>
+          <t>-23,92; 11,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 7,26</t>
+          <t>-5,38; 15,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 10,61</t>
+          <t>-9,99; 12,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,77; 13,2</t>
+          <t>-18,36; 26,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 8,69</t>
+          <t>-6,13; 8,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 8,41</t>
+          <t>-8,11; 9,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-18,76; 9,59</t>
+          <t>-18,68; 8,6</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-15,67%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-4,35%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-67,33%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>29,43%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>10,05%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-16,97%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-15,67%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-4,35%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-66,07%</t>
+          <t>-20,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-46,83%</t>
+          <t>-49,52%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,59; 126,76</t>
+          <t>-53,26; 50,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-39,74; 110,69</t>
+          <t>-48,8; 78,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 180,76</t>
+          <t>-100,0; 93,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-49,43; 49,87</t>
+          <t>-21,77; 117,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,54; 71,24</t>
+          <t>-43,99; 92,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 134,57</t>
+          <t>-100,0; 202,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-26,49; 54,02</t>
+          <t>-26,45; 56,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-33,05; 54,55</t>
+          <t>-34,35; 61,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-88,59; 65,87</t>
+          <t>-88,53; 57,09</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,79</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,88</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,64</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-5,23</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,53</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,2</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,79</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,32</t>
+          <t>2,16</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,34</t>
+          <t>2,38</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 4,12</t>
+          <t>-5,59; 2,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,72; -0,42</t>
+          <t>-3,31; 5,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 10,4</t>
+          <t>-4,67; 12,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 2,95</t>
+          <t>-5,95; 3,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 5,06</t>
+          <t>-9,9; -0,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 11,25</t>
+          <t>-7,08; 12,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 1,99</t>
+          <t>-3,9; 2,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 0,93</t>
+          <t>-4,92; 1,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 7,89</t>
+          <t>-3,94; 9,1</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-6,45%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>15,45%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-2,82%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-23,1%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-6,45%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-22,94; 20,5</t>
+          <t>-25,92; 17,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,62; -1,49</t>
+          <t>-16,22; 31,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-35,27; 47,85</t>
+          <t>-23,24; 70,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,59; 19,16</t>
+          <t>-23,04; 17,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,69; 31,42</t>
+          <t>-39,7; -4,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,58; 66,24</t>
+          <t>-30,85; 58,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 10,66</t>
+          <t>-17,66; 12,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,16; 4,53</t>
+          <t>-22,33; 6,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-20,39; 41,25</t>
+          <t>-18,46; 45,7</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,09</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-4,73</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-7,6</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-10,15</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-4,14</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-16,98</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,09</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-4,73</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-7,66</t>
+          <t>-16,26</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-12,2</t>
+          <t>-11,87</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,03; -1,83</t>
+          <t>-8,61; 7,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 4,06</t>
+          <t>-12,44; 2,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-26,56; -5,29</t>
+          <t>-18,98; 7,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 6,72</t>
+          <t>-17,81; -2,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,73; 2,92</t>
+          <t>-11,94; 5,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,41; 5,33</t>
+          <t>-24,82; -2,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 0,19</t>
+          <t>-11,45; 0,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 1,14</t>
+          <t>-10,87; 1,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-19,48; -2,36</t>
+          <t>-19,17; -2,36</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-4,42%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-19,15%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-30,77%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-36,9%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-15,06%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-61,72%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-4,42%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-19,15%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-31,0%</t>
+          <t>-59,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-46,61%</t>
+          <t>-45,34%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-56,35; -7,12</t>
+          <t>-30,66; 36,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-39,38; 17,53</t>
+          <t>-42,85; 12,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-88,14; -17,25</t>
+          <t>-70,46; 33,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-33,46; 33,34</t>
+          <t>-57,1; -11,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-44,0; 13,55</t>
+          <t>-37,69; 22,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,06; 26,24</t>
+          <t>-83,79; -7,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-39,05; 0,9</t>
+          <t>-38,18; 1,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-35,06; 4,93</t>
+          <t>-36,54; 4,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-69,23; -8,84</t>
+          <t>-69,37; -9,36</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,63</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0,83</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-2,26</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-4,31</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-4,18</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,36</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,63</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,16</t>
+          <t>-2,93</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,65</t>
+          <t>-1,91</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 1,58</t>
+          <t>-5,03; 2,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 0,02</t>
+          <t>-4,41; 2,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 3,55</t>
+          <t>-6,63; 6,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 2,05</t>
+          <t>-6,21; 1,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 2,77</t>
+          <t>-8,2; -0,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 5,41</t>
+          <t>-9,88; 5,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 0,78</t>
+          <t>-4,5; 0,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 0,1</t>
+          <t>-5,08; 0,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 1,95</t>
+          <t>-6,57; 3,06</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-6,72%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-3,12%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-4,11%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-9,7%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-18,44%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-17,91%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-6,72%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-3,12%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-5,74%</t>
+          <t>-12,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-12,18%</t>
+          <t>-8,8%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,09; 7,44</t>
+          <t>-22,61; 12,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-31,69; -0,26</t>
+          <t>-19,55; 13,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-42,69; 15,6</t>
+          <t>-31,11; 31,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-23,26; 11,08</t>
+          <t>-24,46; 7,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,78; 15,27</t>
+          <t>-32,55; -4,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-31,9; 27,98</t>
+          <t>-41,72; 24,5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-18,46; 3,6</t>
+          <t>-19,28; 3,43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-21,88; 0,52</t>
+          <t>-21,63; 0,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-33,55; 9,56</t>
+          <t>-29,02; 14,58</t>
         </is>
       </c>
     </row>
